--- a/data/basedatosPrueba.xlsx
+++ b/data/basedatosPrueba.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="34.5703125" customWidth="1" min="1" max="1"/>
@@ -562,6 +562,33 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Dr.Enrique Alberto Molestina Molestiina</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ALEXANDER FRANCISO TIBANTA MIRANDA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1447586991001</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1447758691</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Dr. Christian Santiago Izurieta Cruz</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
